--- a/01_Thermal/B_results/four_var_analysis.xlsx
+++ b/01_Thermal/B_results/four_var_analysis.xlsx
@@ -493,25 +493,25 @@
         <v>195</v>
       </c>
       <c r="D2" t="n">
-        <v>119.7209658414345</v>
+        <v>114.4186466378758</v>
       </c>
       <c r="E2" t="n">
-        <v>1.48536007537365</v>
+        <v>1.080931622353287</v>
       </c>
       <c r="F2" t="n">
-        <v>9399.908589203438</v>
+        <v>4978.019365383231</v>
       </c>
       <c r="G2" t="n">
         <v>4260.495759386248</v>
       </c>
       <c r="H2" t="n">
-        <v>10.28556846592443</v>
+        <v>5.680987937072524</v>
       </c>
       <c r="I2" t="n">
-        <v>0.4080557081308278</v>
+        <v>0.4994159230013621</v>
       </c>
       <c r="J2" t="n">
-        <v>0.325111012522858</v>
+        <v>0.06037192179767621</v>
       </c>
     </row>
     <row r="3">
@@ -527,25 +527,25 @@
         <v>195</v>
       </c>
       <c r="D3" t="n">
-        <v>87.9439670643153</v>
+        <v>77.06203930312108</v>
       </c>
       <c r="E3" t="n">
-        <v>0.6401154970728339</v>
+        <v>0.6392892782770024</v>
       </c>
       <c r="F3" t="n">
-        <v>2258.893518503264</v>
+        <v>2253.0660207566</v>
       </c>
       <c r="G3" t="n">
         <v>5512.886817461288</v>
       </c>
       <c r="H3" t="n">
-        <v>3.511346309295956</v>
+        <v>3.018107888895867</v>
       </c>
       <c r="I3" t="n">
-        <v>0.7505285367315629</v>
+        <v>0.7425085823731143</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1330205493927246</v>
+        <v>0.01706373521715611</v>
       </c>
     </row>
     <row r="4">
@@ -561,25 +561,25 @@
         <v>195</v>
       </c>
       <c r="D4" t="n">
-        <v>74.68635708195745</v>
+        <v>69.99776964113703</v>
       </c>
       <c r="E4" t="n">
-        <v>0.5000585226641938</v>
+        <v>0.4960270528903175</v>
       </c>
       <c r="F4" t="n">
-        <v>941.8941809623959</v>
+        <v>926.7683060032737</v>
       </c>
       <c r="G4" t="n">
         <v>3766.694924158668</v>
       </c>
       <c r="H4" t="n">
-        <v>3.096271175227074</v>
+        <v>2.716816177795779</v>
       </c>
       <c r="I4" t="n">
-        <v>0.7136616466309362</v>
+        <v>0.7143376832538797</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1395372256056855</v>
+        <v>0.03150455752243763</v>
       </c>
     </row>
     <row r="5">
@@ -595,25 +595,25 @@
         <v>195</v>
       </c>
       <c r="D5" t="n">
-        <v>80.34819759823793</v>
+        <v>72.63133545469029</v>
       </c>
       <c r="E5" t="n">
-        <v>0.6442431274732995</v>
+        <v>0.6648477841652245</v>
       </c>
       <c r="F5" t="n">
-        <v>7112.059191708426</v>
+        <v>7574.260280697753</v>
       </c>
       <c r="G5" t="n">
         <v>17135.46024586532</v>
       </c>
       <c r="H5" t="n">
-        <v>2.096421081335943</v>
+        <v>2.175361366374465</v>
       </c>
       <c r="I5" t="n">
-        <v>0.9252391036065621</v>
+        <v>0.8455170419653861</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1539455274756758</v>
+        <v>0.02998298755819676</v>
       </c>
     </row>
     <row r="6">
@@ -629,25 +629,25 @@
         <v>195</v>
       </c>
       <c r="D6" t="n">
-        <v>72.48682951695935</v>
+        <v>66.18271069583415</v>
       </c>
       <c r="E6" t="n">
-        <v>0.4412539121171183</v>
+        <v>0.4152213895349211</v>
       </c>
       <c r="F6" t="n">
-        <v>1392.289305606081</v>
+        <v>1232.854386024067</v>
       </c>
       <c r="G6" t="n">
         <v>7150.76242849565</v>
       </c>
       <c r="H6" t="n">
-        <v>2.144815841489149</v>
+        <v>1.970391026744906</v>
       </c>
       <c r="I6" t="n">
-        <v>0.9178077209271092</v>
+        <v>0.8998460853134931</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1306087472302757</v>
+        <v>0.02252644167990433</v>
       </c>
     </row>
     <row r="7">
@@ -663,25 +663,25 @@
         <v>195</v>
       </c>
       <c r="D7" t="n">
-        <v>54.55213794349942</v>
+        <v>49.4546352956452</v>
       </c>
       <c r="E7" t="n">
-        <v>0.3653726513169726</v>
+        <v>0.349483763840127</v>
       </c>
       <c r="F7" t="n">
-        <v>908.6637379294934</v>
+        <v>831.3523567569271</v>
       </c>
       <c r="G7" t="n">
         <v>6806.614016268456</v>
       </c>
       <c r="H7" t="n">
-        <v>1.515628152384302</v>
+        <v>1.681549172224897</v>
       </c>
       <c r="I7" t="n">
-        <v>0.892748615629874</v>
+        <v>0.884322622151416</v>
       </c>
       <c r="J7" t="n">
-        <v>0.1801812119594934</v>
+        <v>0.02274668185465609</v>
       </c>
     </row>
     <row r="8">
@@ -697,25 +697,25 @@
         <v>195</v>
       </c>
       <c r="D8" t="n">
-        <v>66.61671727988519</v>
+        <v>59.63210191279779</v>
       </c>
       <c r="E8" t="n">
-        <v>0.3934436124160053</v>
+        <v>0.3516242856519916</v>
       </c>
       <c r="F8" t="n">
-        <v>789.1184233996091</v>
+        <v>630.2820092860975</v>
       </c>
       <c r="G8" t="n">
         <v>5097.734174531417</v>
       </c>
       <c r="H8" t="n">
-        <v>1.023440010884702</v>
+        <v>1.107345606610362</v>
       </c>
       <c r="I8" t="n">
-        <v>1.07473169769869</v>
+        <v>1.012445610696752</v>
       </c>
       <c r="J8" t="n">
-        <v>0.2214939708620011</v>
+        <v>0.03130402284338603</v>
       </c>
     </row>
     <row r="9">
@@ -729,13 +729,13 @@
         <v>1365</v>
       </c>
       <c r="D9" t="n">
-        <v>556.3551723262891</v>
+        <v>509.3792389411014</v>
       </c>
       <c r="E9" t="n">
-        <v>0.6771459494986839</v>
+        <v>0.6087101949930673</v>
       </c>
       <c r="F9" t="n">
-        <v>22802.82694731271</v>
+        <v>18426.60272490795</v>
       </c>
       <c r="G9" t="n">
         <v>49730.64836616704</v>

--- a/01_Thermal/B_results/four_var_analysis.xlsx
+++ b/01_Thermal/B_results/four_var_analysis.xlsx
@@ -493,25 +493,25 @@
         <v>195</v>
       </c>
       <c r="D2" t="n">
-        <v>114.4186466378758</v>
+        <v>114.455257649884</v>
       </c>
       <c r="E2" t="n">
-        <v>1.080931622353287</v>
+        <v>0.7358668072378914</v>
       </c>
       <c r="F2" t="n">
-        <v>4978.019365383231</v>
+        <v>1014.739514454958</v>
       </c>
       <c r="G2" t="n">
-        <v>4260.495759386248</v>
+        <v>1873.942000315514</v>
       </c>
       <c r="H2" t="n">
-        <v>5.680987937072524</v>
+        <v>6.089984553739654</v>
       </c>
       <c r="I2" t="n">
-        <v>0.4994159230013621</v>
+        <v>0.4905950816916237</v>
       </c>
       <c r="J2" t="n">
-        <v>0.06037192179767621</v>
+        <v>0.06191890156730814</v>
       </c>
     </row>
     <row r="3">
@@ -527,25 +527,25 @@
         <v>195</v>
       </c>
       <c r="D3" t="n">
-        <v>77.06203930312108</v>
+        <v>77.25337698317865</v>
       </c>
       <c r="E3" t="n">
-        <v>0.6392892782770024</v>
+        <v>0.3441904166313181</v>
       </c>
       <c r="F3" t="n">
-        <v>2253.0660207566</v>
+        <v>261.6849799945981</v>
       </c>
       <c r="G3" t="n">
-        <v>5512.886817461288</v>
+        <v>2208.926411826067</v>
       </c>
       <c r="H3" t="n">
-        <v>3.018107888895867</v>
+        <v>2.590990713058932</v>
       </c>
       <c r="I3" t="n">
-        <v>0.7425085823731143</v>
+        <v>0.7796530094824001</v>
       </c>
       <c r="J3" t="n">
-        <v>0.01706373521715611</v>
+        <v>0.02044012428254286</v>
       </c>
     </row>
     <row r="4">
@@ -561,25 +561,25 @@
         <v>195</v>
       </c>
       <c r="D4" t="n">
-        <v>69.99776964113703</v>
+        <v>70.16648719729506</v>
       </c>
       <c r="E4" t="n">
-        <v>0.4960270528903175</v>
+        <v>0.535701967987456</v>
       </c>
       <c r="F4" t="n">
-        <v>926.7683060032737</v>
+        <v>592.4328407575952</v>
       </c>
       <c r="G4" t="n">
-        <v>3766.694924158668</v>
+        <v>2064.394253198892</v>
       </c>
       <c r="H4" t="n">
-        <v>2.716816177795779</v>
+        <v>2.712432876171878</v>
       </c>
       <c r="I4" t="n">
-        <v>0.7143376832538797</v>
+        <v>0.6930135884507107</v>
       </c>
       <c r="J4" t="n">
-        <v>0.03150455752243763</v>
+        <v>0.0403261542141832</v>
       </c>
     </row>
     <row r="5">
@@ -595,25 +595,25 @@
         <v>195</v>
       </c>
       <c r="D5" t="n">
-        <v>72.63133545469029</v>
+        <v>72.36635815625394</v>
       </c>
       <c r="E5" t="n">
-        <v>0.6648477841652245</v>
+        <v>0.382234455246192</v>
       </c>
       <c r="F5" t="n">
-        <v>7574.260280697753</v>
+        <v>1147.657980217838</v>
       </c>
       <c r="G5" t="n">
-        <v>17135.46024586532</v>
+        <v>7855.11985311939</v>
       </c>
       <c r="H5" t="n">
-        <v>2.175361366374465</v>
+        <v>2.200196258551008</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8455170419653861</v>
+        <v>0.8247055888652535</v>
       </c>
       <c r="J5" t="n">
-        <v>0.02998298755819676</v>
+        <v>0.03532324719417668</v>
       </c>
     </row>
     <row r="6">
@@ -629,25 +629,25 @@
         <v>195</v>
       </c>
       <c r="D6" t="n">
-        <v>66.18271069583415</v>
+        <v>65.99087911463023</v>
       </c>
       <c r="E6" t="n">
-        <v>0.4152213895349211</v>
+        <v>0.4318126920615021</v>
       </c>
       <c r="F6" t="n">
-        <v>1232.854386024067</v>
+        <v>1033.783965269638</v>
       </c>
       <c r="G6" t="n">
-        <v>7150.76242849565</v>
+        <v>5544.201235342096</v>
       </c>
       <c r="H6" t="n">
-        <v>1.970391026744906</v>
+        <v>1.961755795654303</v>
       </c>
       <c r="I6" t="n">
-        <v>0.8998460853134931</v>
+        <v>0.8826239081779493</v>
       </c>
       <c r="J6" t="n">
-        <v>0.02252644167990433</v>
+        <v>0.02988406223369676</v>
       </c>
     </row>
     <row r="7">
@@ -663,25 +663,25 @@
         <v>195</v>
       </c>
       <c r="D7" t="n">
-        <v>49.4546352956452</v>
+        <v>49.44107938397566</v>
       </c>
       <c r="E7" t="n">
-        <v>0.349483763840127</v>
+        <v>0.3270453618855273</v>
       </c>
       <c r="F7" t="n">
-        <v>831.3523567569271</v>
+        <v>677.7250250101978</v>
       </c>
       <c r="G7" t="n">
-        <v>6806.614016268456</v>
+        <v>6336.326293623866</v>
       </c>
       <c r="H7" t="n">
-        <v>1.681549172224897</v>
+        <v>1.692398814238913</v>
       </c>
       <c r="I7" t="n">
-        <v>0.884322622151416</v>
+        <v>0.8920664806928476</v>
       </c>
       <c r="J7" t="n">
-        <v>0.02274668185465609</v>
+        <v>0.02038055919859889</v>
       </c>
     </row>
     <row r="8">
@@ -697,25 +697,25 @@
         <v>195</v>
       </c>
       <c r="D8" t="n">
-        <v>59.63210191279779</v>
+        <v>59.61630258974568</v>
       </c>
       <c r="E8" t="n">
-        <v>0.3516242856519916</v>
+        <v>0.3794872422763497</v>
       </c>
       <c r="F8" t="n">
-        <v>630.2820092860975</v>
+        <v>783.9624729274146</v>
       </c>
       <c r="G8" t="n">
-        <v>5097.734174531417</v>
+        <v>5443.784362382623</v>
       </c>
       <c r="H8" t="n">
-        <v>1.107345606610362</v>
+        <v>1.110603149290836</v>
       </c>
       <c r="I8" t="n">
-        <v>1.012445610696752</v>
+        <v>1.006027825308475</v>
       </c>
       <c r="J8" t="n">
-        <v>0.03130402284338603</v>
+        <v>0.03303174228086332</v>
       </c>
     </row>
     <row r="9">
@@ -729,16 +729,16 @@
         <v>1365</v>
       </c>
       <c r="D9" t="n">
-        <v>509.3792389411014</v>
+        <v>509.2897410749632</v>
       </c>
       <c r="E9" t="n">
-        <v>0.6087101949930673</v>
+        <v>0.4194660324870697</v>
       </c>
       <c r="F9" t="n">
-        <v>18426.60272490795</v>
+        <v>5511.986778632239</v>
       </c>
       <c r="G9" t="n">
-        <v>49730.64836616704</v>
+        <v>31326.69440980845</v>
       </c>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
